--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,0,1,1</t>
-  </si>
-  <si>
-    <t>0.2480,0.0560,0.0697,0.7130</t>
-  </si>
-  <si>
-    <t>0.0071,0.0053,0.0052,0.9924</t>
-  </si>
-  <si>
-    <t>0.6116,0.0330,0.1213,0.2434</t>
-  </si>
-  <si>
-    <t>0.0288,0.0166,0.0134,0.9710</t>
-  </si>
-  <si>
-    <t>0.9779,0.0138,0.0052,0.0072</t>
-  </si>
-  <si>
-    <t>0.9710,0.0075,0.0015,0.0208</t>
-  </si>
-  <si>
-    <t>0.9479,0.0536,0.0141,0.0053</t>
-  </si>
-  <si>
-    <t>0.9828,0.0085,0.0038,0.0060</t>
-  </si>
-  <si>
-    <t>0.9698,0.0151,0.0066,0.0097</t>
-  </si>
-  <si>
-    <t>0.9517,0.0528,0.0114,0.0058</t>
-  </si>
-  <si>
-    <t>0.9884,0.0085,0.0018,0.0031</t>
-  </si>
-  <si>
-    <t>0.9738,0.0122,0.0037,0.0118</t>
-  </si>
-  <si>
-    <t>0.4397,0.0647,0.6238,0.0352</t>
-  </si>
-  <si>
-    <t>0.1775,0.0390,0.8338,0.0104</t>
-  </si>
-  <si>
-    <t>0.2662,0.0052,0.8727,0.0102</t>
-  </si>
-  <si>
-    <t>0.1165,0.0135,0.9166,0.0109</t>
-  </si>
-  <si>
-    <t>0.3194,0.0463,0.7299,0.0201</t>
-  </si>
-  <si>
-    <t>0.1591,0.7856,0.0764,0.0153</t>
-  </si>
-  <si>
-    <t>0.2996,0.7805,0.0183,0.0068</t>
-  </si>
-  <si>
-    <t>0.5738,0.4445,0.0265,0.0408</t>
-  </si>
-  <si>
-    <t>0.3131,0.7074,0.0391,0.0221</t>
-  </si>
-  <si>
-    <t>0.2752,0.8036,0.0153,0.0092</t>
-  </si>
-  <si>
-    <t>0.0558,0.0156,0.9151,0.0343</t>
-  </si>
-  <si>
-    <t>0.2153,0.0470,0.7953,0.0417</t>
-  </si>
-  <si>
-    <t>0.0261,0.0077,0.9415,0.0396</t>
-  </si>
-  <si>
-    <t>0.1390,0.0128,0.8943,0.0181</t>
-  </si>
-  <si>
-    <t>0.2111,0.0269,0.8326,0.0294</t>
-  </si>
-  <si>
-    <t>0.0291,0.0034,0.9642,0.0153</t>
-  </si>
-  <si>
-    <t>0.0070,0.0017,0.9919,0.0021</t>
-  </si>
-  <si>
-    <t>0.2159,0.7645,0.0502,0.0162</t>
-  </si>
-  <si>
-    <t>0.4685,0.0595,0.6085,0.0422</t>
-  </si>
-  <si>
-    <t>0.0015,0.0025,0.9959,0.0021</t>
-  </si>
-  <si>
-    <t>0.1129,0.3105,0.6507,0.0158</t>
-  </si>
-  <si>
-    <t>0.7759,0.1094,0.0581,0.0679</t>
-  </si>
-  <si>
-    <t>0.2378,0.0844,0.7333,0.0621</t>
-  </si>
-  <si>
-    <t>0.5233,0.5168,0.0340,0.0143</t>
-  </si>
-  <si>
-    <t>0.1315,0.6777,0.3037,0.0300</t>
-  </si>
-  <si>
-    <t>0.0029,0.0243,0.9874,0.0035</t>
-  </si>
-  <si>
-    <t>0.0226,0.1033,0.9295,0.0310</t>
-  </si>
-  <si>
-    <t>0.0189,0.0166,0.9617,0.0159</t>
-  </si>
-  <si>
-    <t>0.0518,0.0211,0.8163,0.1609</t>
-  </si>
-  <si>
-    <t>0.0371,0.0287,0.9572,0.0076</t>
-  </si>
-  <si>
-    <t>0.0036,0.6909,0.8779,0.0023</t>
-  </si>
-  <si>
-    <t>0.0127,0.0112,0.9814,0.0050</t>
-  </si>
-  <si>
-    <t>0.2062,0.0553,0.0850,0.7499</t>
-  </si>
-  <si>
-    <t>0.0444,0.8861,0.1146,0.0314</t>
-  </si>
-  <si>
-    <t>0.0274,0.8671,0.3227,0.0077</t>
-  </si>
-  <si>
-    <t>0.0152,0.9463,0.1375,0.0054</t>
-  </si>
-  <si>
-    <t>0.0008,0.0048,0.9958,0.0024</t>
-  </si>
-  <si>
-    <t>0.0009,0.0066,0.9961,0.0016</t>
-  </si>
-  <si>
-    <t>0.0725,0.0108,0.9318,0.0160</t>
-  </si>
-  <si>
-    <t>0.0208,0.0026,0.9738,0.0094</t>
-  </si>
-  <si>
-    <t>0.0023,0.0020,0.9943,0.0032</t>
-  </si>
-  <si>
-    <t>0.0019,0.0059,0.9941,0.0023</t>
-  </si>
-  <si>
-    <t>0.9295,0.0580,0.0136,0.0104</t>
-  </si>
-  <si>
-    <t>0.9178,0.0933,0.0187,0.0070</t>
-  </si>
-  <si>
-    <t>0.9238,0.0121,0.0044,0.0591</t>
-  </si>
-  <si>
-    <t>0.0008,0.0037,0.9964,0.0023</t>
-  </si>
-  <si>
-    <t>0.9489,0.0220,0.0151,0.0177</t>
-  </si>
-  <si>
-    <t>0.9732,0.0153,0.0047,0.0093</t>
-  </si>
-  <si>
-    <t>0.9763,0.0116,0.0039,0.0087</t>
-  </si>
-  <si>
-    <t>0.0027,0.2571,0.9786,0.0022</t>
-  </si>
-  <si>
-    <t>0.0006,0.0172,0.9957,0.0011</t>
-  </si>
-  <si>
-    <t>0.0027,0.0045,0.9911,0.0061</t>
-  </si>
-  <si>
-    <t>0.0004,0.1074,0.9953,0.0005</t>
-  </si>
-  <si>
-    <t>0.0013,0.0024,0.9962,0.0017</t>
-  </si>
-  <si>
-    <t>0.0188,0.8774,0.2036,0.0019</t>
-  </si>
-  <si>
-    <t>0.0040,0.9793,0.0595,0.0003</t>
-  </si>
-  <si>
-    <t>0.6066,0.0633,0.4898,0.0264</t>
-  </si>
-  <si>
-    <t>0.6481,0.1967,0.1510,0.0669</t>
-  </si>
-  <si>
-    <t>0.0279,0.3154,0.8634,0.0081</t>
-  </si>
-  <si>
-    <t>0.0014,0.1054,0.9895,0.0009</t>
-  </si>
-  <si>
-    <t>0.0044,0.2701,0.9670,0.0031</t>
-  </si>
-  <si>
-    <t>0.0011,0.2544,0.9812,0.0009</t>
-  </si>
-  <si>
-    <t>0.0010,0.0246,0.9941,0.0009</t>
-  </si>
-  <si>
-    <t>0.0215,0.0094,0.0302,0.9671</t>
-  </si>
-  <si>
-    <t>0.0027,0.0057,0.0024,0.9966</t>
-  </si>
-  <si>
-    <t>0.0064,0.0331,0.0089,0.9885</t>
-  </si>
-  <si>
-    <t>0.0658,0.0240,0.0252,0.9371</t>
-  </si>
-  <si>
-    <t>0.0067,0.0077,0.0049,0.9923</t>
-  </si>
-  <si>
-    <t>0.0015,0.0083,0.0166,0.9938</t>
-  </si>
-  <si>
-    <t>0.0046,0.7189,0.8960,0.0031</t>
-  </si>
-  <si>
-    <t>0.0012,0.0471,0.9919,0.0019</t>
-  </si>
-  <si>
-    <t>0.0060,0.0374,0.9797,0.0037</t>
-  </si>
-  <si>
-    <t>0.0028,0.0573,0.9871,0.0021</t>
-  </si>
-  <si>
-    <t>0.0046,0.2100,0.9679,0.0021</t>
-  </si>
-  <si>
-    <t>0.0078,0.3104,0.9375,0.0057</t>
-  </si>
-  <si>
-    <t>0.9690,0.0180,0.0089,0.0072</t>
-  </si>
-  <si>
-    <t>0.9611,0.0369,0.0069,0.0053</t>
-  </si>
-  <si>
-    <t>0.9656,0.0291,0.0054,0.0073</t>
-  </si>
-  <si>
-    <t>0.9784,0.0089,0.0019,0.0096</t>
-  </si>
-  <si>
-    <t>0.9726,0.0249,0.0027,0.0055</t>
-  </si>
-  <si>
-    <t>0.9836,0.0083,0.0058,0.0042</t>
-  </si>
-  <si>
-    <t>0.9761,0.0125,0.0024,0.0086</t>
-  </si>
-  <si>
-    <t>0.9594,0.0240,0.0118,0.0089</t>
-  </si>
-  <si>
-    <t>0.9822,0.0091,0.0026,0.0068</t>
-  </si>
-  <si>
-    <t>0.9832,0.0136,0.0030,0.0041</t>
-  </si>
-  <si>
-    <t>0.9874,0.0086,0.0026,0.0033</t>
-  </si>
-  <si>
-    <t>0.9870,0.0085,0.0026,0.0038</t>
-  </si>
-  <si>
-    <t>0.9875,0.0073,0.0011,0.0047</t>
-  </si>
-  <si>
-    <t>0.9840,0.0099,0.0036,0.0045</t>
-  </si>
-  <si>
-    <t>0.9802,0.0110,0.0027,0.0070</t>
-  </si>
-  <si>
-    <t>0.9650,0.0108,0.0054,0.0199</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9991,0.0007</t>
-  </si>
-  <si>
-    <t>0.0748,0.0120,0.9399,0.0092</t>
-  </si>
-  <si>
-    <t>0.3102,0.0188,0.7006,0.0833</t>
-  </si>
-  <si>
-    <t>0.0913,0.0088,0.9451,0.0061</t>
-  </si>
-  <si>
-    <t>0.1927,0.7768,0.0510,0.0138</t>
-  </si>
-  <si>
-    <t>0.3405,0.6795,0.0375,0.0212</t>
-  </si>
-  <si>
-    <t>0.3679,0.6923,0.0123,0.0262</t>
-  </si>
-  <si>
-    <t>0.2823,0.7581,0.0228,0.0223</t>
-  </si>
-  <si>
-    <t>0.2281,0.7632,0.0552,0.0228</t>
-  </si>
-  <si>
-    <t>0.1710,0.8390,0.0262,0.0064</t>
-  </si>
-  <si>
-    <t>0.6273,0.3969,0.0156,0.0391</t>
-  </si>
-  <si>
-    <t>0.3327,0.2087,0.4955,0.0572</t>
-  </si>
-  <si>
-    <t>0.1155,0.0362,0.6215,0.3294</t>
-  </si>
-  <si>
-    <t>0.4735,0.0890,0.5487,0.0716</t>
-  </si>
-  <si>
-    <t>0.3214,0.0409,0.6871,0.0882</t>
-  </si>
-  <si>
-    <t>0.5222,0.0801,0.2530,0.2465</t>
-  </si>
-  <si>
-    <t>0.0312,0.9006,0.2059,0.0101</t>
-  </si>
-  <si>
-    <t>0.0241,0.9252,0.1340,0.0055</t>
-  </si>
-  <si>
-    <t>0.2245,0.5418,0.1199,0.3064</t>
-  </si>
-  <si>
-    <t>0.0011,0.6245,0.9720,0.0008</t>
-  </si>
-  <si>
-    <t>0.0991,0.7141,0.3267,0.0162</t>
-  </si>
-  <si>
-    <t>0.8141,0.0927,0.0916,0.0238</t>
-  </si>
-  <si>
-    <t>0.5359,0.5201,0.0456,0.0133</t>
-  </si>
-  <si>
-    <t>0.9456,0.0255,0.0266,0.0132</t>
-  </si>
-  <si>
-    <t>0.9712,0.0113,0.0080,0.0089</t>
-  </si>
-  <si>
-    <t>0.9811,0.0109,0.0045,0.0049</t>
-  </si>
-  <si>
-    <t>0.9022,0.0115,0.0076,0.0849</t>
-  </si>
-  <si>
-    <t>0.9657,0.0153,0.0039,0.0160</t>
-  </si>
-  <si>
-    <t>0.9425,0.0182,0.0201,0.0221</t>
-  </si>
-  <si>
-    <t>0.9308,0.0397,0.0221,0.0161</t>
-  </si>
-  <si>
-    <t>0.9783,0.0124,0.0064,0.0064</t>
-  </si>
-  <si>
-    <t>0.0066,0.2839,0.9505,0.0031</t>
-  </si>
-  <si>
-    <t>0.0019,0.1034,0.9885,0.0010</t>
-  </si>
-  <si>
-    <t>0.0024,0.0424,0.9906,0.0011</t>
-  </si>
-  <si>
-    <t>0.0092,0.0245,0.9795,0.0031</t>
-  </si>
-  <si>
-    <t>0.3702,0.0448,0.6792,0.0517</t>
-  </si>
-  <si>
-    <t>0.3726,0.0311,0.6302,0.1016</t>
-  </si>
-  <si>
-    <t>0.1813,0.0101,0.8549,0.0351</t>
-  </si>
-  <si>
-    <t>0.4433,0.0583,0.5673,0.1075</t>
-  </si>
-  <si>
-    <t>0.0997,0.0048,0.0749,0.8278</t>
-  </si>
-  <si>
-    <t>0.0013,0.0052,0.0066,0.9966</t>
-  </si>
-  <si>
-    <t>0.0022,0.0063,0.0072,0.9952</t>
-  </si>
-  <si>
-    <t>0.0132,0.0083,0.0132,0.9830</t>
-  </si>
-  <si>
-    <t>0.0017,0.3051,0.9756,0.0017</t>
-  </si>
-  <si>
-    <t>0.9050,0.0311,0.0075,0.0462</t>
-  </si>
-  <si>
-    <t>0.8504,0.0984,0.0205,0.0372</t>
-  </si>
-  <si>
-    <t>0.9240,0.0226,0.0134,0.0394</t>
-  </si>
-  <si>
-    <t>0.9022,0.0573,0.0126,0.0309</t>
-  </si>
-  <si>
-    <t>0.7958,0.0175,0.0334,0.1653</t>
-  </si>
-  <si>
-    <t>0.3204,0.0192,0.0544,0.6585</t>
-  </si>
-  <si>
-    <t>0.8733,0.0264,0.0083,0.0805</t>
-  </si>
-  <si>
-    <t>0.0069,0.0347,0.9379,0.0771</t>
-  </si>
-  <si>
-    <t>0.2786,0.0071,0.0142,0.7808</t>
-  </si>
-  <si>
-    <t>0.8671,0.0170,0.0424,0.0717</t>
-  </si>
-  <si>
-    <t>0.5661,0.1652,0.2903,0.1356</t>
-  </si>
-  <si>
-    <t>0.3832,0.4526,0.2337,0.0784</t>
-  </si>
-  <si>
-    <t>0.4209,0.2847,0.2954,0.0247</t>
-  </si>
-  <si>
-    <t>0.3310,0.3574,0.1966,0.3337</t>
-  </si>
-  <si>
-    <t>0.5897,0.0871,0.4205,0.0903</t>
-  </si>
-  <si>
-    <t>0.5552,0.2193,0.2385,0.1302</t>
-  </si>
-  <si>
-    <t>0.8799,0.0177,0.0040,0.1078</t>
-  </si>
-  <si>
-    <t>0.9202,0.0255,0.0100,0.0427</t>
-  </si>
-  <si>
-    <t>0.9551,0.0208,0.0031,0.0168</t>
-  </si>
-  <si>
-    <t>0.9406,0.0100,0.0044,0.0432</t>
-  </si>
-  <si>
-    <t>0.9684,0.0103,0.0088,0.0135</t>
-  </si>
-  <si>
-    <t>0.9648,0.0117,0.0024,0.0192</t>
-  </si>
-  <si>
-    <t>0.9462,0.0082,0.0033,0.0454</t>
-  </si>
-  <si>
-    <t>0.9771,0.0063,0.0017,0.0136</t>
-  </si>
-  <si>
-    <t>0.4154,0.6845,0.0160,0.0202</t>
-  </si>
-  <si>
-    <t>0.6758,0.3664,0.0285,0.0161</t>
-  </si>
-  <si>
-    <t>0.7779,0.2450,0.0318,0.0120</t>
-  </si>
-  <si>
-    <t>0.2001,0.0170,0.8883,0.0074</t>
-  </si>
-  <si>
-    <t>0.9257,0.0644,0.0086,0.0144</t>
-  </si>
-  <si>
-    <t>0.8753,0.0780,0.0253,0.0262</t>
-  </si>
-  <si>
-    <t>0.9600,0.0141,0.0056,0.0182</t>
-  </si>
-  <si>
-    <t>0.9123,0.0583,0.0242,0.0213</t>
-  </si>
-  <si>
-    <t>0.0025,0.0240,0.9925,0.0013</t>
-  </si>
-  <si>
-    <t>0.9627,0.0334,0.0071,0.0058</t>
-  </si>
-  <si>
-    <t>0.0014,0.0016,0.9943,0.0050</t>
-  </si>
-  <si>
-    <t>0.0043,0.0361,0.9865,0.0019</t>
-  </si>
-  <si>
-    <t>0.0703,0.0099,0.9388,0.0131</t>
-  </si>
-  <si>
-    <t>0.0007,0.0078,0.9964,0.0010</t>
-  </si>
-  <si>
-    <t>0.0163,0.0131,0.9711,0.0098</t>
-  </si>
-  <si>
-    <t>0.0315,0.0021,0.9794,0.0042</t>
-  </si>
-  <si>
-    <t>0.0041,0.0136,0.9876,0.0044</t>
-  </si>
-  <si>
-    <t>0.2842,0.0126,0.7636,0.0513</t>
-  </si>
-  <si>
-    <t>0.3402,0.0223,0.7795,0.0198</t>
-  </si>
-  <si>
-    <t>0.2397,0.0622,0.7469,0.0194</t>
-  </si>
-  <si>
-    <t>0.3310,0.1449,0.5677,0.0227</t>
-  </si>
-  <si>
-    <t>0.1587,0.1575,0.7198,0.0183</t>
-  </si>
-  <si>
-    <t>0.2141,0.0322,0.8227,0.0170</t>
-  </si>
-  <si>
-    <t>0.2637,0.0882,0.7148,0.0381</t>
-  </si>
-  <si>
-    <t>0.6094,0.0357,0.4680,0.0574</t>
-  </si>
-  <si>
-    <t>0.7354,0.3306,0.0165,0.0132</t>
-  </si>
-  <si>
-    <t>0.9096,0.0993,0.0155,0.0064</t>
-  </si>
-  <si>
-    <t>0.7865,0.2139,0.0300,0.0221</t>
-  </si>
-  <si>
-    <t>0.9275,0.0409,0.0089,0.0238</t>
-  </si>
-  <si>
-    <t>0.9184,0.0819,0.0045,0.0156</t>
-  </si>
-  <si>
-    <t>0.4031,0.0359,0.6397,0.0834</t>
-  </si>
-  <si>
-    <t>0.2643,0.0437,0.7177,0.0899</t>
-  </si>
-  <si>
-    <t>0.3662,0.0132,0.5271,0.1538</t>
-  </si>
-  <si>
-    <t>0.2529,0.0846,0.6661,0.1371</t>
-  </si>
-  <si>
-    <t>0.4017,0.0361,0.5736,0.1156</t>
-  </si>
-  <si>
-    <t>0.1050,0.0559,0.5641,0.3946</t>
-  </si>
-  <si>
-    <t>0.0167,0.0253,0.9541,0.0252</t>
-  </si>
-  <si>
-    <t>0.0087,0.0187,0.9757,0.0106</t>
-  </si>
-  <si>
-    <t>0.0258,0.0749,0.9467,0.0060</t>
-  </si>
-  <si>
-    <t>0.0099,0.0424,0.9699,0.0079</t>
-  </si>
-  <si>
-    <t>0.9688,0.0167,0.0034,0.0106</t>
-  </si>
-  <si>
-    <t>0.9445,0.0366,0.0125,0.0168</t>
-  </si>
-  <si>
-    <t>0.9693,0.0118,0.0029,0.0162</t>
-  </si>
-  <si>
-    <t>0.9775,0.0113,0.0057,0.0073</t>
-  </si>
-  <si>
-    <t>0.9745,0.0114,0.0065,0.0096</t>
-  </si>
-  <si>
-    <t>0.9620,0.0164,0.0034,0.0184</t>
-  </si>
-  <si>
-    <t>0.9242,0.0164,0.0033,0.0591</t>
-  </si>
-  <si>
-    <t>0.9004,0.0231,0.0047,0.0725</t>
-  </si>
-  <si>
-    <t>0.1597,0.0111,0.9045,0.0115</t>
-  </si>
-  <si>
-    <t>0.5421,0.1005,0.4844,0.0539</t>
-  </si>
-  <si>
-    <t>0.7582,0.0698,0.0714,0.1157</t>
-  </si>
-  <si>
-    <t>0.0023,0.0024,0.9950,0.0020</t>
-  </si>
-  <si>
-    <t>0.0006,0.0052,0.9959,0.0021</t>
-  </si>
-  <si>
-    <t>0.0102,0.0076,0.9858,0.0035</t>
-  </si>
-  <si>
-    <t>0.0009,0.0010,0.9963,0.0030</t>
-  </si>
-  <si>
-    <t>0.0488,0.0121,0.9439,0.0127</t>
-  </si>
-  <si>
-    <t>0.0011,0.0052,0.9962,0.0011</t>
-  </si>
-  <si>
-    <t>0.0040,0.0116,0.9825,0.0103</t>
-  </si>
-  <si>
-    <t>0.4323,0.0836,0.5222,0.1158</t>
-  </si>
-  <si>
-    <t>0.3683,0.0210,0.6923,0.0677</t>
-  </si>
-  <si>
-    <t>0.1359,0.0178,0.7809,0.1181</t>
-  </si>
-  <si>
-    <t>0.3978,0.0267,0.5636,0.1285</t>
-  </si>
-  <si>
-    <t>0.9727,0.0122,0.0018,0.0118</t>
-  </si>
-  <si>
-    <t>0.9790,0.0192,0.0035,0.0039</t>
-  </si>
-  <si>
-    <t>0.9762,0.0270,0.0040,0.0032</t>
-  </si>
-  <si>
-    <t>0.8860,0.0722,0.0108,0.0363</t>
-  </si>
-  <si>
-    <t>0.9304,0.0263,0.0082,0.0327</t>
-  </si>
-  <si>
-    <t>0.9743,0.0136,0.0031,0.0094</t>
-  </si>
-  <si>
-    <t>0.9628,0.0241,0.0139,0.0065</t>
-  </si>
-  <si>
-    <t>0.9203,0.0729,0.0076,0.0191</t>
-  </si>
-  <si>
-    <t>0.0076,0.0621,0.9793,0.0013</t>
-  </si>
-  <si>
-    <t>0.0007,0.0050,0.9974,0.0009</t>
-  </si>
-  <si>
-    <t>0.0013,0.0137,0.9943,0.0012</t>
-  </si>
-  <si>
-    <t>0.0954,0.0112,0.9163,0.0152</t>
-  </si>
-  <si>
-    <t>0.0020,0.0028,0.9949,0.0020</t>
-  </si>
-  <si>
-    <t>0.0780,0.0291,0.5028,0.5249</t>
-  </si>
-  <si>
-    <t>0.1009,0.0215,0.8868,0.0280</t>
-  </si>
-  <si>
-    <t>0.0216,0.0248,0.8720,0.1274</t>
-  </si>
-  <si>
-    <t>0.2130,0.0869,0.0599,0.7615</t>
-  </si>
-  <si>
-    <t>0.0074,0.0293,0.0150,0.9839</t>
-  </si>
-  <si>
-    <t>0.0306,0.0071,0.0035,0.9815</t>
-  </si>
-  <si>
-    <t>0.0046,0.0046,0.0034,0.9949</t>
-  </si>
-  <si>
-    <t>0.0075,0.0049,0.0022,0.9937</t>
-  </si>
-  <si>
-    <t>0.5069,0.0519,0.2888,0.2347</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.1639,0.0753,0.0380,0.8349</t>
+  </si>
+  <si>
+    <t>0.0259,0.0238,0.0115,0.9723</t>
+  </si>
+  <si>
+    <t>0.4072,0.0819,0.0197,0.5292</t>
+  </si>
+  <si>
+    <t>0.0494,0.0187,0.0217,0.9496</t>
+  </si>
+  <si>
+    <t>0.9831,0.0173,0.0028,0.0028</t>
+  </si>
+  <si>
+    <t>0.9836,0.0070,0.0018,0.0073</t>
+  </si>
+  <si>
+    <t>0.9571,0.0306,0.0144,0.0063</t>
+  </si>
+  <si>
+    <t>0.9813,0.0094,0.0044,0.0069</t>
+  </si>
+  <si>
+    <t>0.9789,0.0128,0.0025,0.0064</t>
+  </si>
+  <si>
+    <t>0.9817,0.0116,0.0042,0.0045</t>
+  </si>
+  <si>
+    <t>0.9824,0.0140,0.0026,0.0042</t>
+  </si>
+  <si>
+    <t>0.9761,0.0124,0.0035,0.0096</t>
+  </si>
+  <si>
+    <t>0.3762,0.0782,0.6387,0.0512</t>
+  </si>
+  <si>
+    <t>0.0878,0.0126,0.9492,0.0031</t>
+  </si>
+  <si>
+    <t>0.3075,0.0312,0.7800,0.0153</t>
+  </si>
+  <si>
+    <t>0.2798,0.0260,0.7900,0.0154</t>
+  </si>
+  <si>
+    <t>0.4763,0.0474,0.6254,0.0197</t>
+  </si>
+  <si>
+    <t>0.2079,0.8491,0.0197,0.0137</t>
+  </si>
+  <si>
+    <t>0.2379,0.7685,0.0591,0.0175</t>
+  </si>
+  <si>
+    <t>0.7833,0.1557,0.0589,0.0357</t>
+  </si>
+  <si>
+    <t>0.1849,0.8313,0.0374,0.0093</t>
+  </si>
+  <si>
+    <t>0.1433,0.8835,0.0232,0.0149</t>
+  </si>
+  <si>
+    <t>0.1837,0.0817,0.7876,0.0137</t>
+  </si>
+  <si>
+    <t>0.1095,0.0091,0.8664,0.0526</t>
+  </si>
+  <si>
+    <t>0.0315,0.0182,0.9624,0.0089</t>
+  </si>
+  <si>
+    <t>0.0467,0.0129,0.9419,0.0173</t>
+  </si>
+  <si>
+    <t>0.0699,0.0071,0.9345,0.0169</t>
+  </si>
+  <si>
+    <t>0.0318,0.0033,0.9417,0.0311</t>
+  </si>
+  <si>
+    <t>0.0048,0.0046,0.9922,0.0020</t>
+  </si>
+  <si>
+    <t>0.3514,0.4832,0.2234,0.0877</t>
+  </si>
+  <si>
+    <t>0.6375,0.1043,0.3500,0.0591</t>
+  </si>
+  <si>
+    <t>0.0034,0.0058,0.9913,0.0047</t>
+  </si>
+  <si>
+    <t>0.0810,0.6428,0.4159,0.0157</t>
+  </si>
+  <si>
+    <t>0.6455,0.0827,0.0310,0.2516</t>
+  </si>
+  <si>
+    <t>0.1009,0.0277,0.9108,0.0167</t>
+  </si>
+  <si>
+    <t>0.7224,0.2785,0.0395,0.0198</t>
+  </si>
+  <si>
+    <t>0.1378,0.7334,0.2561,0.0436</t>
+  </si>
+  <si>
+    <t>0.0021,0.0342,0.9872,0.0037</t>
+  </si>
+  <si>
+    <t>0.0053,0.0083,0.9843,0.0081</t>
+  </si>
+  <si>
+    <t>0.0030,0.0047,0.9833,0.0148</t>
+  </si>
+  <si>
+    <t>0.0473,0.0073,0.8788,0.0867</t>
+  </si>
+  <si>
+    <t>0.0047,0.0348,0.9861,0.0026</t>
+  </si>
+  <si>
+    <t>0.0083,0.6816,0.8410,0.0070</t>
+  </si>
+  <si>
+    <t>0.0021,0.0097,0.9922,0.0034</t>
+  </si>
+  <si>
+    <t>0.0497,0.0948,0.1150,0.8805</t>
+  </si>
+  <si>
+    <t>0.0202,0.9086,0.1697,0.0212</t>
+  </si>
+  <si>
+    <t>0.0153,0.6003,0.7992,0.0100</t>
+  </si>
+  <si>
+    <t>0.0195,0.9315,0.2197,0.0074</t>
+  </si>
+  <si>
+    <t>0.0010,0.0295,0.9926,0.0018</t>
+  </si>
+  <si>
+    <t>0.0006,0.0104,0.9972,0.0007</t>
+  </si>
+  <si>
+    <t>0.0336,0.0060,0.9748,0.0034</t>
+  </si>
+  <si>
+    <t>0.0402,0.0047,0.9643,0.0085</t>
+  </si>
+  <si>
+    <t>0.0007,0.0017,0.9987,0.0003</t>
+  </si>
+  <si>
+    <t>0.0065,0.0159,0.9873,0.0023</t>
+  </si>
+  <si>
+    <t>0.9446,0.0425,0.0075,0.0134</t>
+  </si>
+  <si>
+    <t>0.9132,0.0566,0.0162,0.0198</t>
+  </si>
+  <si>
+    <t>0.9683,0.0141,0.0072,0.0111</t>
+  </si>
+  <si>
+    <t>0.0500,0.0577,0.9248,0.0137</t>
+  </si>
+  <si>
+    <t>0.9400,0.0414,0.0188,0.0097</t>
+  </si>
+  <si>
+    <t>0.9585,0.0391,0.0053,0.0082</t>
+  </si>
+  <si>
+    <t>0.9412,0.0323,0.0051,0.0210</t>
+  </si>
+  <si>
+    <t>0.0035,0.5310,0.9505,0.0022</t>
+  </si>
+  <si>
+    <t>0.0005,0.0037,0.9975,0.0012</t>
+  </si>
+  <si>
+    <t>0.0039,0.0097,0.9894,0.0038</t>
+  </si>
+  <si>
+    <t>0.0005,0.1293,0.9942,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.0014,0.9983,0.0010</t>
+  </si>
+  <si>
+    <t>0.0516,0.5316,0.5276,0.0127</t>
+  </si>
+  <si>
+    <t>0.0037,0.9869,0.0368,0.0002</t>
+  </si>
+  <si>
+    <t>0.7943,0.0744,0.0833,0.0730</t>
+  </si>
+  <si>
+    <t>0.5490,0.1958,0.3173,0.0504</t>
+  </si>
+  <si>
+    <t>0.0105,0.0228,0.9811,0.0027</t>
+  </si>
+  <si>
+    <t>0.0022,0.2045,0.9810,0.0012</t>
+  </si>
+  <si>
+    <t>0.0067,0.1516,0.9679,0.0029</t>
+  </si>
+  <si>
+    <t>0.0021,0.2550,0.9744,0.0019</t>
+  </si>
+  <si>
+    <t>0.0030,0.1335,0.9801,0.0017</t>
+  </si>
+  <si>
+    <t>0.0103,0.0108,0.0128,0.9852</t>
+  </si>
+  <si>
+    <t>0.0047,0.0089,0.0048,0.9935</t>
+  </si>
+  <si>
+    <t>0.0042,0.0041,0.0052,0.9942</t>
+  </si>
+  <si>
+    <t>0.0097,0.0099,0.0234,0.9806</t>
+  </si>
+  <si>
+    <t>0.0213,0.0078,0.0122,0.9787</t>
+  </si>
+  <si>
+    <t>0.0048,0.0064,0.0064,0.9936</t>
+  </si>
+  <si>
+    <t>0.0043,0.2353,0.9699,0.0019</t>
+  </si>
+  <si>
+    <t>0.0062,0.2352,0.9588,0.0072</t>
+  </si>
+  <si>
+    <t>0.0080,0.0831,0.9706,0.0037</t>
+  </si>
+  <si>
+    <t>0.0025,0.0351,0.9883,0.0041</t>
+  </si>
+  <si>
+    <t>0.0025,0.3679,0.9601,0.0011</t>
+  </si>
+  <si>
+    <t>0.0034,0.2102,0.9734,0.0020</t>
+  </si>
+  <si>
+    <t>0.9679,0.0178,0.0144,0.0066</t>
+  </si>
+  <si>
+    <t>0.9593,0.0109,0.0017,0.0270</t>
+  </si>
+  <si>
+    <t>0.9542,0.0219,0.0130,0.0144</t>
+  </si>
+  <si>
+    <t>0.9756,0.0141,0.0042,0.0087</t>
+  </si>
+  <si>
+    <t>0.9685,0.0134,0.0044,0.0133</t>
+  </si>
+  <si>
+    <t>0.9791,0.0094,0.0018,0.0096</t>
+  </si>
+  <si>
+    <t>0.9579,0.0263,0.0087,0.0110</t>
+  </si>
+  <si>
+    <t>0.9756,0.0133,0.0036,0.0084</t>
+  </si>
+  <si>
+    <t>0.9822,0.0072,0.0015,0.0088</t>
+  </si>
+  <si>
+    <t>0.9833,0.0080,0.0042,0.0057</t>
+  </si>
+  <si>
+    <t>0.9792,0.0094,0.0017,0.0106</t>
+  </si>
+  <si>
+    <t>0.9810,0.0112,0.0038,0.0068</t>
+  </si>
+  <si>
+    <t>0.9813,0.0099,0.0028,0.0065</t>
+  </si>
+  <si>
+    <t>0.9821,0.0131,0.0021,0.0059</t>
+  </si>
+  <si>
+    <t>0.9855,0.0097,0.0025,0.0044</t>
+  </si>
+  <si>
+    <t>0.9744,0.0085,0.0023,0.0139</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9994,0.0005</t>
+  </si>
+  <si>
+    <t>0.0910,0.0449,0.8731,0.0302</t>
+  </si>
+  <si>
+    <t>0.3648,0.0599,0.6433,0.0949</t>
+  </si>
+  <si>
+    <t>0.2710,0.0101,0.7912,0.0397</t>
+  </si>
+  <si>
+    <t>0.2780,0.7737,0.0158,0.0194</t>
+  </si>
+  <si>
+    <t>0.3192,0.6784,0.0425,0.0417</t>
+  </si>
+  <si>
+    <t>0.2462,0.8266,0.0089,0.0096</t>
+  </si>
+  <si>
+    <t>0.4316,0.6864,0.0148,0.0103</t>
+  </si>
+  <si>
+    <t>0.1425,0.8942,0.0090,0.0139</t>
+  </si>
+  <si>
+    <t>0.1571,0.8645,0.0197,0.0081</t>
+  </si>
+  <si>
+    <t>0.5942,0.4772,0.0346,0.0127</t>
+  </si>
+  <si>
+    <t>0.3992,0.2767,0.3758,0.0738</t>
+  </si>
+  <si>
+    <t>0.1130,0.0154,0.9047,0.0171</t>
+  </si>
+  <si>
+    <t>0.3871,0.1081,0.5699,0.0441</t>
+  </si>
+  <si>
+    <t>0.1878,0.0162,0.7301,0.1326</t>
+  </si>
+  <si>
+    <t>0.1905,0.0582,0.1992,0.6387</t>
+  </si>
+  <si>
+    <t>0.0216,0.9303,0.1697,0.0116</t>
+  </si>
+  <si>
+    <t>0.0405,0.9249,0.0698,0.0085</t>
+  </si>
+  <si>
+    <t>0.1070,0.8113,0.1125,0.0311</t>
+  </si>
+  <si>
+    <t>0.0004,0.6193,0.9835,0.0004</t>
+  </si>
+  <si>
+    <t>0.0759,0.7849,0.2257,0.0135</t>
+  </si>
+  <si>
+    <t>0.6912,0.3188,0.0524,0.0117</t>
+  </si>
+  <si>
+    <t>0.6218,0.4229,0.0356,0.0178</t>
+  </si>
+  <si>
+    <t>0.9082,0.0512,0.0289,0.0196</t>
+  </si>
+  <si>
+    <t>0.9658,0.0185,0.0067,0.0107</t>
+  </si>
+  <si>
+    <t>0.9787,0.0127,0.0057,0.0054</t>
+  </si>
+  <si>
+    <t>0.9463,0.0193,0.0169,0.0204</t>
+  </si>
+  <si>
+    <t>0.9733,0.0072,0.0025,0.0160</t>
+  </si>
+  <si>
+    <t>0.7527,0.0791,0.0678,0.1422</t>
+  </si>
+  <si>
+    <t>0.9708,0.0155,0.0105,0.0072</t>
+  </si>
+  <si>
+    <t>0.9710,0.0141,0.0103,0.0065</t>
+  </si>
+  <si>
+    <t>0.0086,0.1166,0.9646,0.0053</t>
+  </si>
+  <si>
+    <t>0.0041,0.1482,0.9767,0.0019</t>
+  </si>
+  <si>
+    <t>0.0008,0.0239,0.9957,0.0009</t>
+  </si>
+  <si>
+    <t>0.0082,0.1097,0.9734,0.0023</t>
+  </si>
+  <si>
+    <t>0.2390,0.0800,0.4103,0.4012</t>
+  </si>
+  <si>
+    <t>0.4369,0.0453,0.4906,0.1469</t>
+  </si>
+  <si>
+    <t>0.2809,0.0139,0.7706,0.0564</t>
+  </si>
+  <si>
+    <t>0.1664,0.0371,0.7920,0.0621</t>
+  </si>
+  <si>
+    <t>0.0100,0.0084,0.0149,0.9844</t>
+  </si>
+  <si>
+    <t>0.0005,0.0040,0.0045,0.9982</t>
+  </si>
+  <si>
+    <t>0.0055,0.0440,0.0100,0.9878</t>
+  </si>
+  <si>
+    <t>0.0147,0.0059,0.0160,0.9811</t>
+  </si>
+  <si>
+    <t>0.0013,0.0770,0.9903,0.0018</t>
+  </si>
+  <si>
+    <t>0.9381,0.0222,0.0040,0.0298</t>
+  </si>
+  <si>
+    <t>0.6394,0.3045,0.0141,0.0677</t>
+  </si>
+  <si>
+    <t>0.8945,0.0497,0.0143,0.0415</t>
+  </si>
+  <si>
+    <t>0.8703,0.0940,0.0162,0.0345</t>
+  </si>
+  <si>
+    <t>0.9324,0.0218,0.0124,0.0280</t>
+  </si>
+  <si>
+    <t>0.1847,0.0213,0.0234,0.8509</t>
+  </si>
+  <si>
+    <t>0.8006,0.0374,0.0082,0.1369</t>
+  </si>
+  <si>
+    <t>0.0033,0.0056,0.9547,0.0947</t>
+  </si>
+  <si>
+    <t>0.4970,0.0172,0.0535,0.4324</t>
+  </si>
+  <si>
+    <t>0.7372,0.0311,0.0166,0.2007</t>
+  </si>
+  <si>
+    <t>0.3955,0.4470,0.0555,0.1901</t>
+  </si>
+  <si>
+    <t>0.3542,0.5446,0.1701,0.1056</t>
+  </si>
+  <si>
+    <t>0.4944,0.2617,0.3394,0.1194</t>
+  </si>
+  <si>
+    <t>0.2915,0.1045,0.6180,0.1028</t>
+  </si>
+  <si>
+    <t>0.6206,0.1548,0.2812,0.0672</t>
+  </si>
+  <si>
+    <t>0.4663,0.4097,0.1728,0.0895</t>
+  </si>
+  <si>
+    <t>0.9559,0.0190,0.0060,0.0182</t>
+  </si>
+  <si>
+    <t>0.9503,0.0264,0.0038,0.0185</t>
+  </si>
+  <si>
+    <t>0.9787,0.0118,0.0028,0.0074</t>
+  </si>
+  <si>
+    <t>0.9261,0.0067,0.0044,0.0754</t>
+  </si>
+  <si>
+    <t>0.9462,0.0296,0.0185,0.0091</t>
+  </si>
+  <si>
+    <t>0.9558,0.0263,0.0164,0.0114</t>
+  </si>
+  <si>
+    <t>0.9733,0.0100,0.0049,0.0116</t>
+  </si>
+  <si>
+    <t>0.9594,0.0122,0.0044,0.0233</t>
+  </si>
+  <si>
+    <t>0.4858,0.6082,0.0181,0.0298</t>
+  </si>
+  <si>
+    <t>0.8497,0.1633,0.0207,0.0150</t>
+  </si>
+  <si>
+    <t>0.5254,0.5227,0.0369,0.0136</t>
+  </si>
+  <si>
+    <t>0.7100,0.1376,0.1992,0.0379</t>
+  </si>
+  <si>
+    <t>0.9397,0.0452,0.0153,0.0087</t>
+  </si>
+  <si>
+    <t>0.9090,0.0463,0.0260,0.0224</t>
+  </si>
+  <si>
+    <t>0.9619,0.0237,0.0095,0.0071</t>
+  </si>
+  <si>
+    <t>0.6771,0.1330,0.0185,0.1590</t>
+  </si>
+  <si>
+    <t>0.0045,0.0067,0.9932,0.0021</t>
+  </si>
+  <si>
+    <t>0.8881,0.0472,0.0124,0.0490</t>
+  </si>
+  <si>
+    <t>0.0072,0.0089,0.9846,0.0051</t>
+  </si>
+  <si>
+    <t>0.0029,0.0205,0.9861,0.0053</t>
+  </si>
+  <si>
+    <t>0.1556,0.0174,0.9024,0.0068</t>
+  </si>
+  <si>
+    <t>0.0036,0.0172,0.9840,0.0080</t>
+  </si>
+  <si>
+    <t>0.0179,0.0092,0.9774,0.0058</t>
+  </si>
+  <si>
+    <t>0.0051,0.0013,0.9937,0.0023</t>
+  </si>
+  <si>
+    <t>0.0063,0.0041,0.9920,0.0021</t>
+  </si>
+  <si>
+    <t>0.4470,0.0718,0.5772,0.0339</t>
+  </si>
+  <si>
+    <t>0.4345,0.0397,0.6431,0.0445</t>
+  </si>
+  <si>
+    <t>0.5184,0.0587,0.3828,0.1573</t>
+  </si>
+  <si>
+    <t>0.2718,0.0326,0.8021,0.0105</t>
+  </si>
+  <si>
+    <t>0.1892,0.0780,0.7772,0.0277</t>
+  </si>
+  <si>
+    <t>0.2265,0.0153,0.8549,0.0170</t>
+  </si>
+  <si>
+    <t>0.3389,0.1033,0.6192,0.0337</t>
+  </si>
+  <si>
+    <t>0.4632,0.0221,0.6216,0.0524</t>
+  </si>
+  <si>
+    <t>0.8404,0.1616,0.0222,0.0133</t>
+  </si>
+  <si>
+    <t>0.5741,0.4855,0.0242,0.0274</t>
+  </si>
+  <si>
+    <t>0.8131,0.1607,0.0637,0.0144</t>
+  </si>
+  <si>
+    <t>0.9551,0.0453,0.0066,0.0072</t>
+  </si>
+  <si>
+    <t>0.8117,0.1818,0.0288,0.0214</t>
+  </si>
+  <si>
+    <t>0.4943,0.1046,0.5034,0.0838</t>
+  </si>
+  <si>
+    <t>0.2956,0.0156,0.7314,0.0724</t>
+  </si>
+  <si>
+    <t>0.2469,0.0416,0.3681,0.4291</t>
+  </si>
+  <si>
+    <t>0.3155,0.0273,0.6962,0.0896</t>
+  </si>
+  <si>
+    <t>0.2632,0.0117,0.5410,0.1964</t>
+  </si>
+  <si>
+    <t>0.0341,0.0359,0.9271,0.0307</t>
+  </si>
+  <si>
+    <t>0.0030,0.0199,0.9896,0.0032</t>
+  </si>
+  <si>
+    <t>0.0078,0.0231,0.9821,0.0050</t>
+  </si>
+  <si>
+    <t>0.0213,0.0462,0.9513,0.0105</t>
+  </si>
+  <si>
+    <t>0.0030,0.0105,0.9853,0.0078</t>
+  </si>
+  <si>
+    <t>0.9596,0.0264,0.0054,0.0119</t>
+  </si>
+  <si>
+    <t>0.9762,0.0194,0.0068,0.0040</t>
+  </si>
+  <si>
+    <t>0.9728,0.0129,0.0040,0.0099</t>
+  </si>
+  <si>
+    <t>0.9768,0.0198,0.0067,0.0045</t>
+  </si>
+  <si>
+    <t>0.9696,0.0153,0.0089,0.0070</t>
+  </si>
+  <si>
+    <t>0.9758,0.0095,0.0030,0.0115</t>
+  </si>
+  <si>
+    <t>0.9642,0.0141,0.0027,0.0185</t>
+  </si>
+  <si>
+    <t>0.9607,0.0163,0.0074,0.0152</t>
+  </si>
+  <si>
+    <t>0.3196,0.0193,0.7636,0.0440</t>
+  </si>
+  <si>
+    <t>0.6182,0.0214,0.5900,0.0139</t>
+  </si>
+  <si>
+    <t>0.5950,0.1079,0.3552,0.1451</t>
+  </si>
+  <si>
+    <t>0.0072,0.0035,0.9902,0.0031</t>
+  </si>
+  <si>
+    <t>0.0014,0.0030,0.9959,0.0015</t>
+  </si>
+  <si>
+    <t>0.0169,0.0182,0.9716,0.0061</t>
+  </si>
+  <si>
+    <t>0.0005,0.0009,0.9987,0.0005</t>
+  </si>
+  <si>
+    <t>0.0614,0.0384,0.9216,0.0088</t>
+  </si>
+  <si>
+    <t>0.0005,0.0018,0.9979,0.0009</t>
+  </si>
+  <si>
+    <t>0.0047,0.0157,0.9883,0.0022</t>
+  </si>
+  <si>
+    <t>0.2219,0.0444,0.8023,0.0152</t>
+  </si>
+  <si>
+    <t>0.5136,0.0357,0.5567,0.0727</t>
+  </si>
+  <si>
+    <t>0.2550,0.0042,0.8266,0.0320</t>
+  </si>
+  <si>
+    <t>0.2264,0.0333,0.3584,0.4457</t>
+  </si>
+  <si>
+    <t>0.9772,0.0090,0.0023,0.0113</t>
+  </si>
+  <si>
+    <t>0.9817,0.0089,0.0036,0.0067</t>
+  </si>
+  <si>
+    <t>0.9793,0.0147,0.0046,0.0042</t>
+  </si>
+  <si>
+    <t>0.9717,0.0154,0.0073,0.0076</t>
+  </si>
+  <si>
+    <t>0.9520,0.0265,0.0044,0.0162</t>
+  </si>
+  <si>
+    <t>0.9697,0.0182,0.0140,0.0047</t>
+  </si>
+  <si>
+    <t>0.9577,0.0208,0.0063,0.0186</t>
+  </si>
+  <si>
+    <t>0.9521,0.0091,0.0018,0.0385</t>
+  </si>
+  <si>
+    <t>0.0375,0.0987,0.9023,0.0140</t>
+  </si>
+  <si>
+    <t>0.0015,0.0047,0.9961,0.0010</t>
+  </si>
+  <si>
+    <t>0.0029,0.0061,0.9941,0.0014</t>
+  </si>
+  <si>
+    <t>0.0644,0.0345,0.9323,0.0092</t>
+  </si>
+  <si>
+    <t>0.0017,0.0015,0.9972,0.0011</t>
+  </si>
+  <si>
+    <t>0.0388,0.0151,0.7568,0.3062</t>
+  </si>
+  <si>
+    <t>0.1491,0.0526,0.8460,0.0254</t>
+  </si>
+  <si>
+    <t>0.0338,0.0191,0.9172,0.0501</t>
+  </si>
+  <si>
+    <t>0.1391,0.0090,0.0080,0.9143</t>
+  </si>
+  <si>
+    <t>0.0343,0.0319,0.0495,0.9414</t>
+  </si>
+  <si>
+    <t>0.0864,0.0184,0.0190,0.9297</t>
+  </si>
+  <si>
+    <t>0.0056,0.0095,0.0117,0.9899</t>
+  </si>
+  <si>
+    <t>0.0034,0.0060,0.0038,0.9955</t>
+  </si>
+  <si>
+    <t>0.5324,0.0319,0.4484,0.1159</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1965,7 @@
         <v>260</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2133,7 @@
         <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2189,7 @@
         <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2231,7 @@
         <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2273,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2287,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,10 +2410,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2441,7 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2483,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2553,7 @@
         <v>263</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,7 +2581,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,10 +2606,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,10 +2816,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>261</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,10 +2886,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2959,7 @@
         <v>261</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2973,7 @@
         <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2987,7 @@
         <v>261</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3001,7 @@
         <v>261</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,10 +3096,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3113,7 @@
         <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3127,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3141,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3155,7 @@
         <v>261</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3169,7 @@
         <v>261</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3435,7 @@
         <v>261</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3547,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3558,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3589,7 @@
         <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3603,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3614,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3841,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3855,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,10 +3894,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3908,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3939,7 @@
         <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4009,7 @@
         <v>261</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4037,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4093,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,10 +4132,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4160,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,10 +4174,10 @@
         <v>259</v>
       </c>
       <c r="C160" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,10 +4188,10 @@
         <v>259</v>
       </c>
       <c r="C161" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,10 +4230,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4359,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4384,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4639,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4653,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4667,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4681,7 @@
         <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4779,7 @@
         <v>261</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4793,7 @@
         <v>261</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,10 +4804,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4821,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4835,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5182,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5199,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,10 +5210,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5406,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5451,7 @@
         <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
